--- a/appendix/Риски_приложение_реестр_TableMind.xlsx
+++ b/appendix/Риски_приложение_реестр_TableMind.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Карта рисков" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр рисков'!$A$4:$W$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">'Реестр рисков'!$A$4:$W$23</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="252">
   <si>
     <t xml:space="preserve">Наименование проекта: TableMind — AI-сервис проверки Excel-моделей (веб-аудит + надстройка Excel)</t>
   </si>
@@ -424,6 +424,21 @@
   </si>
   <si>
     <t xml:space="preserve">10.0, 14.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Искажение структуры, стилей или диаграмм xlsx при экспорте исправленного файла</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Пользователь получает повреждённую книгу, потеря доверия к исправлениям</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регрессионный тест «до/после экспорта» показывает отличия вне исправленных ячеек</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Точечная правка XML внутри исходного пакета xlsx вместо пересохранения; регрессионный тест экспорта; проверка открытия в Excel для Windows, Mac и веб</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0, 9.0</t>
   </si>
   <si>
     <t xml:space="preserve">Временная недоступность провайдера LLM</t>
@@ -2836,7 +2851,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:srgbClr val="548235"/>
+              <a:srgbClr val="bf8f00"/>
             </a:solidFill>
             <a:ln w="47520">
               <a:noFill/>
@@ -2847,7 +2862,7 @@
             <c:size val="9"/>
             <c:spPr>
               <a:solidFill>
-                <a:srgbClr val="548235"/>
+                <a:srgbClr val="bf8f00"/>
               </a:solidFill>
             </c:spPr>
           </c:marker>
@@ -2899,6 +2914,92 @@
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
+                  <c:v>0.5</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="1"/>
+        </c:ser>
+        <c:ser>
+          <c:idx val="18"/>
+          <c:order val="18"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>"R19"</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>R19</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:srgbClr val="548235"/>
+            </a:solidFill>
+            <a:ln w="47520">
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="9"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="548235"/>
+              </a:solidFill>
+            </c:spPr>
+          </c:marker>
+          <c:dLbls>
+            <c:txPr>
+              <a:bodyPr wrap="square"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr b="0" sz="1000" spc="-1" strike="noStrike">
+                    <a:solidFill>
+                      <a:srgbClr val="000000"/>
+                    </a:solidFill>
+                    <a:latin typeface="Calibri"/>
+                  </a:defRPr>
+                </a:pPr>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="r"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="0"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="1"/>
+            <c:showPercent val="0"/>
+            <c:separator>; </c:separator>
+            <c:showLeaderLines val="1"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:showLeaderLines val="1"/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Реестр рисков'!$G$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>0.4</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Реестр рисков'!$H$23</c:f>
+              <c:numCache>
+                <c:formatCode>0.00</c:formatCode>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
                   <c:v>0.3</c:v>
                 </c:pt>
               </c:numCache>
@@ -2906,11 +3007,11 @@
           </c:yVal>
           <c:smooth val="1"/>
         </c:ser>
-        <c:axId val="96806908"/>
-        <c:axId val="25487130"/>
+        <c:axId val="73693822"/>
+        <c:axId val="30939885"/>
       </c:scatterChart>
       <c:valAx>
-        <c:axId val="96806908"/>
+        <c:axId val="73693822"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1"/>
@@ -2988,13 +3089,13 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25487130"/>
+        <c:crossAx val="30939885"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
       </c:valAx>
       <c:valAx>
-        <c:axId val="25487130"/>
+        <c:axId val="30939885"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="1.05"/>
@@ -3072,7 +3173,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96806908"/>
+        <c:crossAx val="73693822"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
         <c:majorUnit val="0.2"/>
@@ -3320,7 +3421,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:W40"/>
+  <dimension ref="A1:W41"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3499,7 +3600,7 @@
         <v>Средний</v>
       </c>
       <c r="W5" s="4" t="n">
-        <f aca="false">RANK(I5,$I$5:$I$22)+COUNTIF($I$5:I5,I5)-1</f>
+        <f aca="false">RANK(I5,$I$5:$I$23)+COUNTIF($I$5:I5,I5)-1</f>
         <v>2</v>
       </c>
     </row>
@@ -3578,7 +3679,7 @@
         <v>Средний</v>
       </c>
       <c r="W6" s="4" t="n">
-        <f aca="false">RANK(I6,$I$5:$I$22)+COUNTIF($I$5:I6,I6)-1</f>
+        <f aca="false">RANK(I6,$I$5:$I$23)+COUNTIF($I$5:I6,I6)-1</f>
         <v>4</v>
       </c>
     </row>
@@ -3657,7 +3758,7 @@
         <v>Средний</v>
       </c>
       <c r="W7" s="4" t="n">
-        <f aca="false">RANK(I7,$I$5:$I$22)+COUNTIF($I$5:I7,I7)-1</f>
+        <f aca="false">RANK(I7,$I$5:$I$23)+COUNTIF($I$5:I7,I7)-1</f>
         <v>1</v>
       </c>
     </row>
@@ -3736,7 +3837,7 @@
         <v>Средний</v>
       </c>
       <c r="W8" s="4" t="n">
-        <f aca="false">RANK(I8,$I$5:$I$22)+COUNTIF($I$5:I8,I8)-1</f>
+        <f aca="false">RANK(I8,$I$5:$I$23)+COUNTIF($I$5:I8,I8)-1</f>
         <v>3</v>
       </c>
     </row>
@@ -3815,7 +3916,7 @@
         <v>Средний</v>
       </c>
       <c r="W9" s="4" t="n">
-        <f aca="false">RANK(I9,$I$5:$I$22)+COUNTIF($I$5:I9,I9)-1</f>
+        <f aca="false">RANK(I9,$I$5:$I$23)+COUNTIF($I$5:I9,I9)-1</f>
         <v>5</v>
       </c>
     </row>
@@ -3894,7 +3995,7 @@
         <v>Средний</v>
       </c>
       <c r="W10" s="4" t="n">
-        <f aca="false">RANK(I10,$I$5:$I$22)+COUNTIF($I$5:I10,I10)-1</f>
+        <f aca="false">RANK(I10,$I$5:$I$23)+COUNTIF($I$5:I10,I10)-1</f>
         <v>6</v>
       </c>
     </row>
@@ -3973,7 +4074,7 @@
         <v>Низкий</v>
       </c>
       <c r="W11" s="4" t="n">
-        <f aca="false">RANK(I11,$I$5:$I$22)+COUNTIF($I$5:I11,I11)-1</f>
+        <f aca="false">RANK(I11,$I$5:$I$23)+COUNTIF($I$5:I11,I11)-1</f>
         <v>8</v>
       </c>
     </row>
@@ -4052,7 +4153,7 @@
         <v>Средний</v>
       </c>
       <c r="W12" s="4" t="n">
-        <f aca="false">RANK(I12,$I$5:$I$22)+COUNTIF($I$5:I12,I12)-1</f>
+        <f aca="false">RANK(I12,$I$5:$I$23)+COUNTIF($I$5:I12,I12)-1</f>
         <v>9</v>
       </c>
     </row>
@@ -4131,7 +4232,7 @@
         <v>Средний</v>
       </c>
       <c r="W13" s="4" t="n">
-        <f aca="false">RANK(I13,$I$5:$I$22)+COUNTIF($I$5:I13,I13)-1</f>
+        <f aca="false">RANK(I13,$I$5:$I$23)+COUNTIF($I$5:I13,I13)-1</f>
         <v>7</v>
       </c>
     </row>
@@ -4210,7 +4311,7 @@
         <v>Средний</v>
       </c>
       <c r="W14" s="4" t="n">
-        <f aca="false">RANK(I14,$I$5:$I$22)+COUNTIF($I$5:I14,I14)-1</f>
+        <f aca="false">RANK(I14,$I$5:$I$23)+COUNTIF($I$5:I14,I14)-1</f>
         <v>13</v>
       </c>
     </row>
@@ -4289,7 +4390,7 @@
         <v>Низкий</v>
       </c>
       <c r="W15" s="4" t="n">
-        <f aca="false">RANK(I15,$I$5:$I$22)+COUNTIF($I$5:I15,I15)-1</f>
+        <f aca="false">RANK(I15,$I$5:$I$23)+COUNTIF($I$5:I15,I15)-1</f>
         <v>10</v>
       </c>
     </row>
@@ -4368,7 +4469,7 @@
         <v>Низкий</v>
       </c>
       <c r="W16" s="4" t="n">
-        <f aca="false">RANK(I16,$I$5:$I$22)+COUNTIF($I$5:I16,I16)-1</f>
+        <f aca="false">RANK(I16,$I$5:$I$23)+COUNTIF($I$5:I16,I16)-1</f>
         <v>14</v>
       </c>
     </row>
@@ -4447,7 +4548,7 @@
         <v>Низкий</v>
       </c>
       <c r="W17" s="4" t="n">
-        <f aca="false">RANK(I17,$I$5:$I$22)+COUNTIF($I$5:I17,I17)-1</f>
+        <f aca="false">RANK(I17,$I$5:$I$23)+COUNTIF($I$5:I17,I17)-1</f>
         <v>11</v>
       </c>
     </row>
@@ -4526,7 +4627,7 @@
         <v>Низкий</v>
       </c>
       <c r="W18" s="4" t="n">
-        <f aca="false">RANK(I18,$I$5:$I$22)+COUNTIF($I$5:I18,I18)-1</f>
+        <f aca="false">RANK(I18,$I$5:$I$23)+COUNTIF($I$5:I18,I18)-1</f>
         <v>12</v>
       </c>
     </row>
@@ -4605,7 +4706,7 @@
         <v>Низкий</v>
       </c>
       <c r="W19" s="4" t="n">
-        <f aca="false">RANK(I19,$I$5:$I$22)+COUNTIF($I$5:I19,I19)-1</f>
+        <f aca="false">RANK(I19,$I$5:$I$23)+COUNTIF($I$5:I19,I19)-1</f>
         <v>15</v>
       </c>
     </row>
@@ -4684,7 +4785,7 @@
         <v>Низкий</v>
       </c>
       <c r="W20" s="4" t="n">
-        <f aca="false">RANK(I20,$I$5:$I$22)+COUNTIF($I$5:I20,I20)-1</f>
+        <f aca="false">RANK(I20,$I$5:$I$23)+COUNTIF($I$5:I20,I20)-1</f>
         <v>16</v>
       </c>
     </row>
@@ -4763,8 +4864,8 @@
         <v>Низкий</v>
       </c>
       <c r="W21" s="4" t="n">
-        <f aca="false">RANK(I21,$I$5:$I$22)+COUNTIF($I$5:I21,I21)-1</f>
-        <v>17</v>
+        <f aca="false">RANK(I21,$I$5:$I$23)+COUNTIF($I$5:I21,I21)-1</f>
+        <v>18</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -4791,47 +4892,47 @@
         <v>0.4</v>
       </c>
       <c r="H22" s="7" t="n">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="I22" s="8" t="n">
         <f aca="false">G22*H22</f>
-        <v>0.12</v>
+        <v>0.2</v>
       </c>
       <c r="J22" s="4" t="str">
         <f aca="false">IF(I22&gt;'Шкалы оценки'!$B$21,"Высокий",IF(I22&gt;='Шкалы оценки'!$B$22,"Средний","Низкий"))</f>
-        <v>Низкий</v>
+        <v>Средний</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>81</v>
+        <v>29</v>
       </c>
       <c r="L22" s="6" t="s">
         <v>130</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="N22" s="4" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="O22" s="9" t="n">
-        <v>6000</v>
+        <v>20000</v>
       </c>
       <c r="P22" s="10" t="n">
         <f aca="false">G22*O22</f>
-        <v>2400</v>
+        <v>8000</v>
       </c>
       <c r="Q22" s="9" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="R22" s="6" t="str">
         <f aca="false">IF(K22="Принятие","Принятие: покрывается резервом",IF(Q22&lt;P22,"Оправданы (затраты &lt; ожид. потерь)","Пересмотреть меры"))</f>
-        <v>Принятие: покрывается резервом</v>
+        <v>Оправданы (затраты &lt; ожид. потерь)</v>
       </c>
       <c r="S22" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="T22" s="7" t="n">
         <v>0.4</v>
-      </c>
-      <c r="T22" s="7" t="n">
-        <v>0.2</v>
       </c>
       <c r="U22" s="8" t="n">
         <f aca="false">S22*T22</f>
@@ -4842,159 +4943,218 @@
         <v>Низкий</v>
       </c>
       <c r="W22" s="4" t="n">
-        <f aca="false">RANK(I22,$I$5:$I$22)+COUNTIF($I$5:I22,I22)-1</f>
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C23" s="11" t="s">
-        <v>131</v>
-      </c>
-      <c r="P23" s="12" t="n">
-        <f aca="false">SUM(P5:P22)</f>
-        <v>315100</v>
-      </c>
-      <c r="Q23" s="12" t="n">
-        <f aca="false">SUM(Q5:Q22)</f>
-        <v>58500</v>
+        <f aca="false">RANK(I22,$I$5:$I$23)+COUNTIF($I$5:I22,I22)-1</f>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="B23" s="5" t="str">
+        <f aca="false">"R"&amp;A23</f>
+        <v>R19</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G23" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="H23" s="7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <f aca="false">G23*H23</f>
+        <v>0.12</v>
+      </c>
+      <c r="J23" s="4" t="str">
+        <f aca="false">IF(I23&gt;'Шкалы оценки'!$B$21,"Высокий",IF(I23&gt;='Шкалы оценки'!$B$22,"Средний","Низкий"))</f>
+        <v>Низкий</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="L23" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="M23" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N23" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="O23" s="9" t="n">
+        <v>6000</v>
+      </c>
+      <c r="P23" s="10" t="n">
+        <f aca="false">G23*O23</f>
+        <v>2400</v>
+      </c>
+      <c r="Q23" s="9" t="n">
+        <v>1500</v>
+      </c>
+      <c r="R23" s="6" t="str">
+        <f aca="false">IF(K23="Принятие","Принятие: покрывается резервом",IF(Q23&lt;P23,"Оправданы (затраты &lt; ожид. потерь)","Пересмотреть меры"))</f>
+        <v>Принятие: покрывается резервом</v>
+      </c>
+      <c r="S23" s="7" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T23" s="7" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="U23" s="8" t="n">
+        <f aca="false">S23*T23</f>
+        <v>0.08</v>
+      </c>
+      <c r="V23" s="4" t="str">
+        <f aca="false">IF(U23&gt;'Шкалы оценки'!$B$21,"Высокий",IF(U23&gt;='Шкалы оценки'!$B$22,"Средний","Низкий"))</f>
+        <v>Низкий</v>
+      </c>
+      <c r="W23" s="4" t="n">
+        <f aca="false">RANK(I23,$I$5:$I$23)+COUNTIF($I$5:I23,I23)-1</f>
+        <v>19</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C24" s="13" t="s">
-        <v>132</v>
+      <c r="C24" s="11" t="s">
+        <v>136</v>
+      </c>
+      <c r="P24" s="12" t="n">
+        <f aca="false">SUM(P5:P23)</f>
+        <v>323100</v>
+      </c>
+      <c r="Q24" s="12" t="n">
+        <f aca="false">SUM(Q5:Q23)</f>
+        <v>60500</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D25" s="5" t="n">
-        <f aca="false">COUNTIF(J5:J22,"Высокий")</f>
-        <v>4</v>
+      <c r="C25" s="13" t="s">
+        <v>137</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C26" s="14" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="D26" s="5" t="n">
-        <f aca="false">COUNTIF(J5:J22,"Средний")</f>
-        <v>12</v>
+        <f aca="false">COUNTIF(J5:J23,"Высокий")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C27" s="14" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="D27" s="5" t="n">
-        <f aca="false">COUNTIF(J5:J22,"Низкий")</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(J5:J23,"Средний")</f>
+        <v>13</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C28" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <f aca="false">AVERAGE(I5:I22)</f>
-        <v>0.332222222222222</v>
+        <v>140</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <f aca="false">COUNTIF(J5:J23,"Низкий")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C29" s="14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="D29" s="15" t="n">
-        <f aca="false">AVERAGE(U5:U22)</f>
-        <v>0.145555555555556</v>
+        <f aca="false">AVERAGE(I5:I23)</f>
+        <v>0.325263157894737</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C30" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D30" s="16" t="n">
-        <f aca="false">1-SUM(U5:U22)/SUM(I5:I22)</f>
-        <v>0.561872909698997</v>
+        <v>142</v>
+      </c>
+      <c r="D30" s="15" t="n">
+        <f aca="false">AVERAGE(U5:U23)</f>
+        <v>0.142105263157895</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C31" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D31" s="17" t="n">
-        <f aca="false">Q23</f>
-        <v>58500</v>
+        <v>143</v>
+      </c>
+      <c r="D31" s="16" t="n">
+        <f aca="false">1-SUM(U5:U23)/SUM(I5:I23)</f>
+        <v>0.563106796116505</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C32" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D32" s="18" t="n">
-        <v>47000</v>
+        <v>144</v>
+      </c>
+      <c r="D32" s="17" t="n">
+        <f aca="false">Q24</f>
+        <v>60500</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C33" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D33" s="17" t="n">
-        <f aca="false">SUMIF(K5:K22,"Принятие",P5:P22)</f>
-        <v>12400</v>
+        <v>145</v>
+      </c>
+      <c r="D33" s="18" t="n">
+        <v>47000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C34" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D34" s="5" t="str">
-        <f aca="false">IF(D33&lt;=D32,"ДА","НЕТ")</f>
+        <v>146</v>
+      </c>
+      <c r="D34" s="17" t="n">
+        <f aca="false">SUMIF(K5:K23,"Принятие",P5:P23)</f>
+        <v>12400</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C35" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="D35" s="5" t="str">
+        <f aca="false">IF(D34&lt;=D33,"ДА","НЕТ")</f>
         <v>ДА</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C36" s="13" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="E37" s="3" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C37" s="13" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="E38" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="F37" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="C38" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="E38" s="6" t="s">
+      <c r="F38" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="F38" s="8" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="G38" s="6" t="s">
+      <c r="G38" s="3" t="s">
         <v>153</v>
       </c>
     </row>
@@ -5012,7 +5172,7 @@
         <v>157</v>
       </c>
       <c r="F39" s="8" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="G39" s="6" t="s">
         <v>158</v>
@@ -5032,15 +5192,35 @@
         <v>162</v>
       </c>
       <c r="F40" s="8" t="n">
-        <v>0.6</v>
+        <v>0.3</v>
       </c>
       <c r="G40" s="6" t="s">
         <v>163</v>
       </c>
     </row>
+    <row r="41" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B41" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="F41" s="8" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G41" s="6" t="s">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:W22"/>
-  <conditionalFormatting sqref="J5:J22">
+  <autoFilter ref="A4:W23"/>
+  <conditionalFormatting sqref="J5:J23">
     <cfRule type="cellIs" priority="2" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Высокий"</formula>
     </cfRule>
@@ -5051,7 +5231,7 @@
       <formula>"Низкий"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V5:V22">
+  <conditionalFormatting sqref="V5:V23">
     <cfRule type="cellIs" priority="5" operator="equal" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>"Высокий"</formula>
     </cfRule>
@@ -5063,7 +5243,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K22" type="list">
+    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K5:K23" type="list">
       <formula1>"Уклонение,Снижение,Передача,Принятие,Снижение + передача"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -5097,228 +5277,228 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>165</v>
+        <v>170</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>168</v>
+        <v>173</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="4" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="4" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="4" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="11" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="4" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="E13" s="6" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="4" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="4" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="E15" s="6" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="E16" s="6" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="4" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="19" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -5326,48 +5506,48 @@
         <v>11</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="19" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="B21" s="7" t="n">
         <v>0.505</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="20" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="B22" s="7" t="n">
         <v>0.14</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="21" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B23" s="7" t="n">
         <v>0</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="22" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="B25" s="22"/>
       <c r="C25" s="22"/>
@@ -5412,64 +5592,64 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="23" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="24" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B5" s="25" t="n">
         <v>1</v>
       </c>
       <c r="C5" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D5" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R16</v>
       </c>
       <c r="E5" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F5" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="G5" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H5" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I5" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J5" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K5" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L5" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5479,43 +5659,43 @@
         <v>0.9</v>
       </c>
       <c r="C6" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D6" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E6" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R13</v>
       </c>
       <c r="F6" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="G6" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H6" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R2</v>
       </c>
       <c r="I6" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R3</v>
       </c>
       <c r="J6" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K6" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L6" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.9)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.9)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.9)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.9)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.9)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.9)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.9)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.9)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.9)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.9)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.9)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.9)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.9)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.9)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.9)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.9)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.9)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.9)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.9)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5525,43 +5705,43 @@
         <v>0.8</v>
       </c>
       <c r="C7" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D7" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E7" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R12</v>
       </c>
       <c r="F7" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R7</v>
       </c>
       <c r="G7" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R5</v>
       </c>
       <c r="H7" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I7" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R1</v>
       </c>
       <c r="J7" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K7" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L7" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.8)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.8)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.8)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.8)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.8)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.8)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.8)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.8)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.8)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.8)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.8)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.8)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.8)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.8)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.8)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.8)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.8)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.8)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.8)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5571,43 +5751,43 @@
         <v>0.7</v>
       </c>
       <c r="C8" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R11</v>
       </c>
       <c r="G8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R9</v>
       </c>
       <c r="H8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I8" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J8" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R4</v>
       </c>
       <c r="K8" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L8" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.7)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.7)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.7)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.7)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.7)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.7)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.7)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.7)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.7)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.7)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.7)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.7)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.7)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.7)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.7)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.7)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.7)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.7)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.7)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5617,43 +5797,43 @@
         <v>0.6</v>
       </c>
       <c r="C9" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D9" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R17</v>
       </c>
       <c r="E9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R10</v>
       </c>
       <c r="G9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R8</v>
       </c>
       <c r="H9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R6</v>
       </c>
       <c r="I9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J9" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K9" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L9" s="28" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.6)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.6)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.6)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.6)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.6)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.6)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.6)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.6)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.6)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.6)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.6)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.6)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.6)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.6)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.6)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.6)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.6)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.6)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.6)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5663,43 +5843,43 @@
         <v>0.5</v>
       </c>
       <c r="C10" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D10" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
-        <v/>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
+        <v>R18</v>
       </c>
       <c r="G10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R14</v>
       </c>
       <c r="H10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L10" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.5)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.5)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.5)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.5)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.5)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.5)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.5)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.5)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.5)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.5)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.5)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.5)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.5)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.5)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.5)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.5)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.5)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.5)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.5)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5709,43 +5889,43 @@
         <v>0.4</v>
       </c>
       <c r="C11" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D11" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E11" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="G11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v>R15</v>
       </c>
       <c r="I11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L11" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.4)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.4)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.4)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.4)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.4)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.4)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.4)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.4)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.4)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.4)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.4)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.4)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.4)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.4)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.4)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.4)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.4)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.4)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.4)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5755,43 +5935,43 @@
         <v>0.3</v>
       </c>
       <c r="C12" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D12" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E12" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F12" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
-        <v>R18</v>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
+        <v>R19</v>
       </c>
       <c r="G12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L12" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.3)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.3)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.3)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.3)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.3)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.3)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.3)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.3)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.3)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.3)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.3)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.3)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.3)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.3)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.3)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.3)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.3)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.3)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.3)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5801,43 +5981,43 @@
         <v>0.2</v>
       </c>
       <c r="C13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="G13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H13" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I13" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J13" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K13" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L13" s="27" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.2)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.2)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.2)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.2)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.2)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.2)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.2)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.2)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.2)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.2)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.2)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.2)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.2)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.2)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.2)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.2)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.2)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.2)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.2)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5847,43 +6027,43 @@
         <v>0.1</v>
       </c>
       <c r="C14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="D14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.2)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.2)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.2)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.2)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.2)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.2)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.2)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.2)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.2)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.2)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.2)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.2)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.2)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.2)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.2)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.2)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.2)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.2)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.2)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="E14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.3)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.3)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.3)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.3)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.3)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.3)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.3)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.3)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.3)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.3)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.3)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.3)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.3)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.3)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.3)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.3)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.3)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.3)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.3)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="F14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.4)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.4)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.4)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.4)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.4)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.4)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.4)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.4)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.4)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.4)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.4)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.4)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.4)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.4)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.4)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.4)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.4)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.4)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.4)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="G14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.5)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.5)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.5)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.5)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.5)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.5)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.5)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.5)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.5)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.5)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.5)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.5)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.5)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.5)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.5)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.5)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.5)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.5)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.5)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="H14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.6)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.6)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.6)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.6)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.6)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.6)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.6)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.6)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.6)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.6)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.6)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.6)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.6)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.6)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.6)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.6)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.6)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.6)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.6)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="I14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.7)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.7)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.7)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.7)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.7)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.7)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.7)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.7)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.7)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.7)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.7)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.7)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.7)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.7)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.7)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.7)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.7)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.7)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.7)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="J14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.8)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.8)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.8)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.8)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.8)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.8)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.8)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.8)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.8)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.8)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.8)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.8)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.8)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.8)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.8)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.8)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.8)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.8)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.8)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="K14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-0.9)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-0.9)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-0.9)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-0.9)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-0.9)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-0.9)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-0.9)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-0.9)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-0.9)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-0.9)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-0.9)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-0.9)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-0.9)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-0.9)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-0.9)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-0.9)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-0.9)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-0.9)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-0.9)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
       <c r="L14" s="26" t="str">
-        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ",""))</f>
+        <f aca="false">TRIM(IF(AND(ABS('Реестр рисков'!$G$5-1)&lt;0.001,ABS('Реестр рисков'!$H$5-0.1)&lt;0.001),'Реестр рисков'!$B$5&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$6-1)&lt;0.001,ABS('Реестр рисков'!$H$6-0.1)&lt;0.001),'Реестр рисков'!$B$6&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$7-1)&lt;0.001,ABS('Реестр рисков'!$H$7-0.1)&lt;0.001),'Реестр рисков'!$B$7&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$8-1)&lt;0.001,ABS('Реестр рисков'!$H$8-0.1)&lt;0.001),'Реестр рисков'!$B$8&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$9-1)&lt;0.001,ABS('Реестр рисков'!$H$9-0.1)&lt;0.001),'Реестр рисков'!$B$9&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$10-1)&lt;0.001,ABS('Реестр рисков'!$H$10-0.1)&lt;0.001),'Реестр рисков'!$B$10&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$11-1)&lt;0.001,ABS('Реестр рисков'!$H$11-0.1)&lt;0.001),'Реестр рисков'!$B$11&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$12-1)&lt;0.001,ABS('Реестр рисков'!$H$12-0.1)&lt;0.001),'Реестр рисков'!$B$12&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$13-1)&lt;0.001,ABS('Реестр рисков'!$H$13-0.1)&lt;0.001),'Реестр рисков'!$B$13&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$14-1)&lt;0.001,ABS('Реестр рисков'!$H$14-0.1)&lt;0.001),'Реестр рисков'!$B$14&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$15-1)&lt;0.001,ABS('Реестр рисков'!$H$15-0.1)&lt;0.001),'Реестр рисков'!$B$15&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$16-1)&lt;0.001,ABS('Реестр рисков'!$H$16-0.1)&lt;0.001),'Реестр рисков'!$B$16&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$17-1)&lt;0.001,ABS('Реестр рисков'!$H$17-0.1)&lt;0.001),'Реестр рисков'!$B$17&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$18-1)&lt;0.001,ABS('Реестр рисков'!$H$18-0.1)&lt;0.001),'Реестр рисков'!$B$18&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$19-1)&lt;0.001,ABS('Реестр рисков'!$H$19-0.1)&lt;0.001),'Реестр рисков'!$B$19&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$20-1)&lt;0.001,ABS('Реестр рисков'!$H$20-0.1)&lt;0.001),'Реестр рисков'!$B$20&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$21-1)&lt;0.001,ABS('Реестр рисков'!$H$21-0.1)&lt;0.001),'Реестр рисков'!$B$21&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$22-1)&lt;0.001,ABS('Реестр рисков'!$H$22-0.1)&lt;0.001),'Реестр рисков'!$B$22&amp;" ","")&amp;IF(AND(ABS('Реестр рисков'!$G$23-1)&lt;0.001,ABS('Реестр рисков'!$H$23-0.1)&lt;0.001),'Реестр рисков'!$B$23&amp;" ",""))</f>
         <v/>
       </c>
     </row>
@@ -5921,7 +6101,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="C16" s="29" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D16" s="29"/>
       <c r="E16" s="29"/>
@@ -5936,24 +6116,24 @@
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="30"/>
       <c r="C18" s="31" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="32"/>
       <c r="C19" s="31" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="33"/>
       <c r="C20" s="31" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="34" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="C22" s="34"/>
       <c r="D22" s="34"/>
@@ -5966,10 +6146,10 @@
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
@@ -5977,7 +6157,7 @@
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="J23" s="3" t="s">
         <v>11</v>
@@ -5988,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="C24" s="6" t="str">
-        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$22,MATCH(B24,'Реестр рисков'!$W$5:$W$22,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$22,MATCH(B24,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$23,MATCH(B24,'Реестр рисков'!$W$5:$W$23,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$23,MATCH(B24,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>R3 — Пользователи не захотят менять привычную работу в Excel и пробовать новый сервис</v>
       </c>
       <c r="D24" s="6"/>
@@ -5997,7 +6177,7 @@
       <c r="G24" s="6"/>
       <c r="H24" s="6"/>
       <c r="I24" s="8" t="n">
-        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$22,MATCH(B24,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$23,MATCH(B24,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>0.63</v>
       </c>
       <c r="J24" s="4" t="str">
@@ -6010,7 +6190,7 @@
         <v>2</v>
       </c>
       <c r="C25" s="6" t="str">
-        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$22,MATCH(B25,'Реестр рисков'!$W$5:$W$22,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$22,MATCH(B25,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$23,MATCH(B25,'Реестр рисков'!$W$5:$W$23,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$23,MATCH(B25,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>R1 — Крупные платформы (Microsoft Copilot, ChatGPT / Claude for Excel) выпустят бесплатный «режим проверки»</v>
       </c>
       <c r="D25" s="6"/>
@@ -6019,7 +6199,7 @@
       <c r="G25" s="6"/>
       <c r="H25" s="6"/>
       <c r="I25" s="8" t="n">
-        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$22,MATCH(B25,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$23,MATCH(B25,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>0.56</v>
       </c>
       <c r="J25" s="4" t="str">
@@ -6032,7 +6212,7 @@
         <v>3</v>
       </c>
       <c r="C26" s="6" t="str">
-        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$22,MATCH(B26,'Реестр рисков'!$W$5:$W$22,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$22,MATCH(B26,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$23,MATCH(B26,'Реестр рисков'!$W$5:$W$23,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$23,MATCH(B26,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>R4 — Срыв сроков критического пути из-за недооценки трудоёмкости (ядро, надстройка)</v>
       </c>
       <c r="D26" s="6"/>
@@ -6041,7 +6221,7 @@
       <c r="G26" s="6"/>
       <c r="H26" s="6"/>
       <c r="I26" s="8" t="n">
-        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$22,MATCH(B26,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$23,MATCH(B26,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>0.56</v>
       </c>
       <c r="J26" s="4" t="str">
@@ -6054,7 +6234,7 @@
         <v>4</v>
       </c>
       <c r="C27" s="6" t="str">
-        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$22,MATCH(B27,'Реестр рисков'!$W$5:$W$22,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$22,MATCH(B27,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$23,MATCH(B27,'Реестр рисков'!$W$5:$W$23,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$23,MATCH(B27,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>R2 — Высокая доля ложных срабатываний правил (precision критичных находок &lt; 90%)</v>
       </c>
       <c r="D27" s="6"/>
@@ -6063,7 +6243,7 @@
       <c r="G27" s="6"/>
       <c r="H27" s="6"/>
       <c r="I27" s="8" t="n">
-        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$22,MATCH(B27,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$23,MATCH(B27,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>0.54</v>
       </c>
       <c r="J27" s="4" t="str">
@@ -6076,7 +6256,7 @@
         <v>5</v>
       </c>
       <c r="C28" s="6" t="str">
-        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$22,MATCH(B28,'Реестр рисков'!$W$5:$W$22,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$22,MATCH(B28,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$B$5:$B$23,MATCH(B28,'Реестр рисков'!$W$5:$W$23,0))&amp;" — "&amp;INDEX('Реестр рисков'!$C$5:$C$23,MATCH(B28,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>R5 — Пользователи не готовы загружать конфиденциальные финмодели в облако</v>
       </c>
       <c r="D28" s="6"/>
@@ -6085,7 +6265,7 @@
       <c r="G28" s="6"/>
       <c r="H28" s="6"/>
       <c r="I28" s="8" t="n">
-        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$22,MATCH(B28,'Реестр рисков'!$W$5:$W$22,0))</f>
+        <f aca="false">INDEX('Реестр рисков'!$I$5:$I$23,MATCH(B28,'Реестр рисков'!$W$5:$W$23,0))</f>
         <v>0.4</v>
       </c>
       <c r="J28" s="4" t="str">

--- a/appendix/Риски_приложение_реестр_TableMind.xlsx
+++ b/appendix/Риски_приложение_реестр_TableMind.xlsx
@@ -444,7 +444,7 @@
     <t xml:space="preserve">Временная недоступность провайдера LLM</t>
   </si>
   <si>
-    <t xml:space="preserve">Нет AI-объяснений и Cmd-K на время сбоя</t>
+    <t xml:space="preserve">Нет AI-объяснений и исправлений на время сбоя</t>
   </si>
   <si>
     <t xml:space="preserve">Ошибки или таймауты API &gt; 5% за час</t>

--- a/appendix/Риски_приложение_реестр_TableMind.xlsx
+++ b/appendix/Риски_приложение_реестр_TableMind.xlsx
@@ -366,7 +366,7 @@
     <t xml:space="preserve">Замечания валидации AppSource; проверка дольше 4 недель</t>
   </si>
   <si>
-    <t xml:space="preserve">Подача за 6 недель до запуска, прохождение чек-листа валидации, веб-аудит как независимый канал продаж</t>
+    <t xml:space="preserve">Чек-лист валидации AppSource проходится на бете 13.0 и в тестировании 14.0; подача — в первый день работы 15.0 (01.09.2027), проверка до 4 недель укладывается в месяц работы; при задержке публичный запуск идёт через веб-аудит, надстройка публикуется позже</t>
   </si>
   <si>
     <t xml:space="preserve">Фронтенд-разработчик</t>

--- a/appendix/Риски_приложение_реестр_TableMind.xlsx
+++ b/appendix/Риски_приложение_реестр_TableMind.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Отставание &gt; 2 недель от базового плана на воротах</t>
   </si>
   <si>
-    <t xml:space="preserve">Ворота фаз, еженедельный контроль по диаграмме Ганта, MoSCoW — перенос Should в v2, AI-агенты для типового кода</t>
+    <t xml:space="preserve">Ворота фаз, еженедельный контроль по диаграмме Ганта; при отставании более 2 недель — второй бэкенд-разработчик и подрядчик на критические работы за счёт резерва; AI-агенты для типового кода; Should и Could в план не входят, объём Must не расширяется</t>
   </si>
   <si>
     <t xml:space="preserve">Руководитель проекта</t>

--- a/appendix/Риски_приложение_реестр_TableMind.xlsx
+++ b/appendix/Риски_приложение_реестр_TableMind.xlsx
@@ -378,7 +378,7 @@
     <t xml:space="preserve">Раздувание требований (собственный редактор, коннекторы, Google Sheets)</t>
   </si>
   <si>
-    <t xml:space="preserve">Распыление ресурсов, срыв сроков MVP</t>
+    <t xml:space="preserve">Распыление ресурсов, задержка MVP до 2 недель</t>
   </si>
   <si>
     <t xml:space="preserve">Запросы вне списка Must/Should от заказчика и бета-пользователей</t>
